--- a/public/更新賃料検討_入力シート_記入例_麻布十番.xlsx
+++ b/public/更新賃料検討_入力シート_記入例_麻布十番.xlsx
@@ -92,7 +92,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -105,10 +105,6 @@
     <xf numFmtId="3" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -549,49 +545,89 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>麻布十番ロイヤルプレイス 604号室</t>
         </is>
       </c>
-      <c r="B2" s="9" t="n">
+      <c r="B2" s="5" t="n">
         <v>210000</v>
       </c>
-      <c r="C2" s="9" t="n">
+      <c r="C2" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D2" s="10" t="n">
+      <c r="D2" s="6" t="n">
         <v>38.1</v>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>東京都港区麻布十番2-1-1</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>東京メトロ南北線</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>麻布十番</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>2005-09</t>
+        </is>
+      </c>
+      <c r="J2" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>● の付いた列は必須です。2行目は記入例なので消してから使ってください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>麻布十番ロイヤルプレイス 604号室</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="n">
+        <v>210000</v>
+      </c>
+      <c r="C3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="8" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>東京都港区麻布十番</t>
         </is>
       </c>
-      <c r="F2" s="8" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>東京メトロ南北線・都営大江戸線</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>麻布十番</t>
         </is>
       </c>
-      <c r="H2" s="11" t="n">
+      <c r="H3" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="I2" s="8" t="n"/>
-      <c r="J2" s="11" t="n">
+      <c r="I3" s="8" t="n"/>
+      <c r="J3" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>● の付いた列は必須です。2行目は記入例なので消してから使ってください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
       <c r="L3" s="3" t="inlineStr">
         <is>
           <t>金額はすべて税込。家賃と管理費は分けて入れ、アプリが合算した月額総額で計算する。</t>
@@ -637,7 +673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -711,274 +747,316 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>カスタリア麻布十番 705号室</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>280000</v>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>42.84</v>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>東京都港区麻布十番2-10-1</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>東京メトロ南北線</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>麻布十番</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>2005-09</t>
+        </is>
+      </c>
+      <c r="J2" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>● の付いた列は必須です。2行目は記入例なので消してから使ってください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>アーバンパーク麻布十番 0902号室</t>
         </is>
       </c>
-      <c r="B2" s="9" t="n">
+      <c r="B3" s="8" t="n">
         <v>310000</v>
       </c>
-      <c r="C2" s="9" t="n">
+      <c r="C3" s="8" t="n">
         <v>10000</v>
       </c>
-      <c r="D2" s="10" t="n">
+      <c r="D3" s="8" t="n">
         <v>42.14</v>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>東京都港区麻布十番2-12-12</t>
         </is>
       </c>
-      <c r="F2" s="8" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>東京メトロ南北線</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>麻布十番</t>
         </is>
       </c>
-      <c r="H2" s="11" t="n">
+      <c r="H3" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I2" s="8" t="inlineStr">
+      <c r="I3" s="8" t="inlineStr">
         <is>
           <t>1999-11</t>
         </is>
       </c>
-      <c r="J2" s="11" t="n">
+      <c r="J3" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>● の付いた列は必須です。2行目は記入例なので消してから使ってください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>金額はすべて税込。家賃と管理費は分けて入れ、アプリが合算した月額総額で計算する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>カスタリア麻布十番 705号室</t>
         </is>
       </c>
-      <c r="B3" s="12" t="n">
+      <c r="B4" s="8" t="n">
         <v>280000</v>
       </c>
-      <c r="C3" s="12" t="n">
+      <c r="C4" s="8" t="n">
         <v>10000</v>
       </c>
-      <c r="D3" s="12" t="n">
+      <c r="D4" s="8" t="n">
         <v>42.84</v>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>東京都港区麻布十番2-10-1</t>
         </is>
       </c>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>東京メトロ南北線</t>
         </is>
       </c>
-      <c r="G3" s="12" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>麻布十番</t>
         </is>
       </c>
-      <c r="H3" s="12" t="n">
+      <c r="H4" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I3" s="12" t="inlineStr">
+      <c r="I4" s="8" t="inlineStr">
         <is>
           <t>2005-09</t>
         </is>
       </c>
-      <c r="J3" s="12" t="n">
+      <c r="J4" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>金額はすべて税込。家賃と管理費は分けて入れ、アプリが合算した月額総額で計算する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>・賃料: 税込・月額。管理費は含めない</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>カスタリア麻布十番 603号室</t>
         </is>
       </c>
-      <c r="B4" s="12" t="n">
+      <c r="B5" s="8" t="n">
         <v>241000</v>
       </c>
-      <c r="C4" s="12" t="n">
+      <c r="C5" s="8" t="n">
         <v>10000</v>
       </c>
-      <c r="D4" s="12" t="n">
+      <c r="D5" s="8" t="n">
         <v>36.95</v>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>東京都港区麻布十番2-10-1</t>
         </is>
       </c>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>東京メトロ南北線</t>
         </is>
       </c>
-      <c r="G4" s="12" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>麻布十番</t>
         </is>
       </c>
-      <c r="H4" s="12" t="n">
+      <c r="H5" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I4" s="12" t="inlineStr">
+      <c r="I5" s="8" t="inlineStr">
         <is>
           <t>2005-09</t>
         </is>
       </c>
-      <c r="J4" s="12" t="n">
+      <c r="J5" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>・賃料: 税込・月額。管理費は含めない</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>・管理費: 共益費を含む。無ければ0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>南麻布1-5-8 702号室</t>
         </is>
       </c>
-      <c r="B5" s="12" t="n">
+      <c r="B6" s="8" t="n">
         <v>185000</v>
       </c>
-      <c r="C5" s="12" t="n">
+      <c r="C6" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="12" t="n">
+      <c r="D6" s="8" t="n">
         <v>39</v>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>東京都港区南麻布1-5-8</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>東京メトロ南北線</t>
         </is>
       </c>
-      <c r="G5" s="12" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>麻布十番</t>
         </is>
       </c>
-      <c r="H5" s="12" t="n">
+      <c r="H6" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="I5" s="12" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>1970</t>
         </is>
       </c>
-      <c r="J5" s="12" t="n">
+      <c r="J6" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>・管理費: 共益費を含む。無ければ0</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>メゾン東麻布 401号室</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B7" s="8" t="n">
         <v>178000</v>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C7" s="8" t="n">
         <v>12000</v>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="D7" s="8" t="n">
         <v>38</v>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>東京都港区東麻布2-22-10</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>都営大江戸線</t>
         </is>
       </c>
-      <c r="G6" s="12" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>赤羽橋</t>
         </is>
       </c>
-      <c r="H6" s="12" t="n">
+      <c r="H7" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I6" s="12" t="inlineStr">
+      <c r="I7" s="8" t="inlineStr">
         <is>
           <t>1983</t>
         </is>
       </c>
-      <c r="J6" s="12" t="n">
+      <c r="J7" s="8" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>イイダアネックス麻布十番 501号室</t>
         </is>
       </c>
-      <c r="B7" s="12" t="n">
+      <c r="B8" s="8" t="n">
         <v>170000</v>
       </c>
-      <c r="C7" s="12" t="n">
+      <c r="C8" s="8" t="n">
         <v>5000</v>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="D8" s="8" t="n">
         <v>43.06</v>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>東京都港区東麻布3-7-8</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>東京メトロ南北線</t>
         </is>
       </c>
-      <c r="G7" s="12" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>麻布十番</t>
         </is>
       </c>
-      <c r="H7" s="12" t="n">
+      <c r="H8" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="I7" s="12" t="inlineStr">
+      <c r="I8" s="8" t="inlineStr">
         <is>
           <t>1992-08</t>
         </is>
       </c>
-      <c r="J7" s="12" t="n">
+      <c r="J8" s="8" t="n">
         <v>5</v>
       </c>
     </row>

--- a/public/更新賃料検討_入力シート_記入例_麻布十番.xlsx
+++ b/public/更新賃料検討_入力シート_記入例_麻布十番.xlsx
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -484,7 +484,13 @@
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="56" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="56" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -538,7 +544,37 @@
           <t>所在階</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>間取り</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>契約用途</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>改装時期</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>改装内容</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>家具の有無</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>前回更新日</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
         <is>
           <t>更新を検討している部屋。1行だけ記入する。</t>
         </is>
@@ -585,7 +621,37 @@
       <c r="J2" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>1LDK</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>居住用（事務所使用可）</t>
+        </is>
+      </c>
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="N2" s="4" t="inlineStr">
+        <is>
+          <t>洗面台・浴室・フローリング交換</t>
+        </is>
+      </c>
+      <c r="O2" s="4" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="P2" s="4" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="R2" s="3" t="inlineStr">
         <is>
           <t>● の付いた列は必須です。2行目は記入例なので消してから使ってください。</t>
         </is>
@@ -628,37 +694,66 @@
       <c r="J3" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="K3" s="8" t="inlineStr">
+        <is>
+          <t>1LDK</t>
+        </is>
+      </c>
+      <c r="L3" s="8" t="inlineStr">
+        <is>
+          <t>居住用（事務所使用可）</t>
+        </is>
+      </c>
+      <c r="M3" s="8" t="n"/>
+      <c r="N3" s="8" t="n"/>
+      <c r="O3" s="8" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="P3" s="8" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
         <is>
           <t>金額はすべて税込。家賃と管理費は分けて入れ、アプリが合算した月額総額で計算する。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="L4" s="3" t="inlineStr">
+      <c r="R4" s="3" t="inlineStr">
         <is>
           <t>・現在家賃: 税込・月額。管理費は含めない</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="L5" s="3" t="inlineStr">
+      <c r="R5" s="3" t="inlineStr">
         <is>
           <t>・現在管理費: 税込・月額。無ければ0</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="L6" s="3" t="inlineStr">
+      <c r="R6" s="3" t="inlineStr">
         <is>
           <t>・面積(㎡): 専有・契約・壁芯の別は区別しない</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="L7" s="3" t="inlineStr">
+      <c r="R7" s="3" t="inlineStr">
         <is>
           <t>・築年月: YYYY-MM または YYYY</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>・前回更新日: 「前回から◯年据え置き」を説明に使う</t>
         </is>
       </c>
     </row>
@@ -673,7 +768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -686,7 +781,12 @@
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="56" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="34" customWidth="1" min="15" max="15"/>
+    <col width="56" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -740,9 +840,34 @@
           <t>所在階</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
-        <is>
-          <t>周辺の募集図面から転記する。査定賃料の自動算出には5件以上が必要。ここに入れた行はすべて集計対象になるので、条件の合わない物件は入れないこと。</t>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>募集元  ●</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>確認日  ●</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>出典</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>本住戸との共通点</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>賃料差の要因</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>周辺の募集図面から転記する。査定賃料の自動算出には5件以上が必要。ここに入れた行はすべて集計対象になるので、条件の合わない物件は入れないこと。算定に使った事例はすべて借主向け資料に掲載されるため、募集元と確認日は必須。</t>
         </is>
       </c>
     </row>
@@ -787,7 +912,32 @@
       <c r="J2" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>株式会社モリモトクオリティ</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>募集図面 p.2 / https://…</t>
+        </is>
+      </c>
+      <c r="N2" s="4" t="inlineStr">
+        <is>
+          <t>同一駅徒歩3分圏・1LDK・40㎡前後</t>
+        </is>
+      </c>
+      <c r="O2" s="4" t="inlineStr">
+        <is>
+          <t>築6年新しく、オートロック・宅配ボックスあり</t>
+        </is>
+      </c>
+      <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>● の付いた列は必須です。2行目は記入例なので消してから使ってください。</t>
         </is>
@@ -834,7 +984,32 @@
       <c r="J3" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="K3" s="8" t="inlineStr">
+        <is>
+          <t>三菱地所ハウスネット</t>
+        </is>
+      </c>
+      <c r="L3" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M3" s="8" t="inlineStr">
+        <is>
+          <t>募集図面 p.1</t>
+        </is>
+      </c>
+      <c r="N3" s="8" t="inlineStr">
+        <is>
+          <t>同一駅徒歩3分圏・1LDK・42㎡台</t>
+        </is>
+      </c>
+      <c r="O3" s="8" t="inlineStr">
+        <is>
+          <t>築7年新しい。2026年6月に洗面台・浴室・建具・床を改装済み</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
         <is>
           <t>金額はすべて税込。家賃と管理費は分けて入れ、アプリが合算した月額総額で計算する。</t>
         </is>
@@ -881,7 +1056,32 @@
       <c r="J4" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="K4" s="8" t="inlineStr">
+        <is>
+          <t>株式会社モリモトクオリティ</t>
+        </is>
+      </c>
+      <c r="L4" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M4" s="8" t="inlineStr">
+        <is>
+          <t>募集図面 p.2</t>
+        </is>
+      </c>
+      <c r="N4" s="8" t="inlineStr">
+        <is>
+          <t>同一駅徒歩3分圏・1LDK・42㎡台</t>
+        </is>
+      </c>
+      <c r="O4" s="8" t="inlineStr">
+        <is>
+          <t>築13年新しい。オートロック・宅配ボックス・床暖房あり。最上階</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
         <is>
           <t>・賃料: 税込・月額。管理費は含めない</t>
         </is>
@@ -928,7 +1128,32 @@
       <c r="J5" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="K5" s="8" t="inlineStr">
+        <is>
+          <t>株式会社モリモトクオリティ</t>
+        </is>
+      </c>
+      <c r="L5" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M5" s="8" t="inlineStr">
+        <is>
+          <t>募集図面 p.5</t>
+        </is>
+      </c>
+      <c r="N5" s="8" t="inlineStr">
+        <is>
+          <t>同一駅徒歩3分圏・1LDK・同一階層</t>
+        </is>
+      </c>
+      <c r="O5" s="8" t="inlineStr">
+        <is>
+          <t>築13年新しい。面積は1.15㎡狭い。オートロック・宅配ボックスあり</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
         <is>
           <t>・管理費: 共益費を含む。無ければ0</t>
         </is>
@@ -975,6 +1200,36 @@
       <c r="J6" s="8" t="n">
         <v>7</v>
       </c>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>三井のリハウス 赤坂支店</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t>募集図面 p.7</t>
+        </is>
+      </c>
+      <c r="N6" s="8" t="inlineStr">
+        <is>
+          <t>同一駅徒歩4分・39㎡・最上階</t>
+        </is>
+      </c>
+      <c r="O6" s="8" t="inlineStr">
+        <is>
+          <t>築48年古い。管理費の設定なし。設備はエアコン・トイレのみの記載</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>・募集元: 借主が自分で確認できるようにするため必須</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
@@ -1017,6 +1272,36 @@
       <c r="J7" s="8" t="n">
         <v>4</v>
       </c>
+      <c r="K7" s="8" t="inlineStr">
+        <is>
+          <t>（募集図面に記載）</t>
+        </is>
+      </c>
+      <c r="L7" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M7" s="8" t="inlineStr">
+        <is>
+          <t>募集図面 p.8</t>
+        </is>
+      </c>
+      <c r="N7" s="8" t="inlineStr">
+        <is>
+          <t>1LDK・38㎡で面積がほぼ同じ</t>
+        </is>
+      </c>
+      <c r="O7" s="8" t="inlineStr">
+        <is>
+          <t>築35年古い。最寄りが赤羽橋。エレベーターあり・4階建の最上階</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>・確認日: 募集条件を確認した日。必須</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
@@ -1058,6 +1343,31 @@
       </c>
       <c r="J8" s="8" t="n">
         <v>5</v>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>株式会社ワールドインベストメンツ</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t>募集図面 p.9</t>
+        </is>
+      </c>
+      <c r="N8" s="8" t="inlineStr">
+        <is>
+          <t>同一駅徒歩2分・43㎡</t>
+        </is>
+      </c>
+      <c r="O8" s="8" t="inlineStr">
+        <is>
+          <t>築26年古い。2DKで居室構成が異なる。エレベーターなし</t>
+        </is>
       </c>
     </row>
   </sheetData>
